--- a/public/xlsx/pta-school-separation-school-survey.xlsx
+++ b/public/xlsx/pta-school-separation-school-survey.xlsx
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>docs/guideline.md 第4章</t>
+          <t>docs/guideline.md 第3章</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>docs/guideline.md 第4章</t>
+          <t>docs/guideline.md 第3章</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>docs/guideline.md 第5章</t>
+          <t>docs/guideline.md 第2章</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>文科省通知M001と併用。目的外使用は当然利用ではないことを説明</t>
+          <t>地方自治法238条の4第7項及び文科省通知M001と併用。目的外使用は当然利用ではないことを説明</t>
         </is>
       </c>
     </row>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>docs/guideline.md 第6章</t>
+          <t>docs/guideline.md 第9章</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>docs/guideline.md 第6章</t>
+          <t>docs/guideline.md 第8章・第10章</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>docs/guideline.md 第7章</t>
+          <t>docs/guideline.md 第5章</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>docs/guideline.md 第7章</t>
+          <t>docs/guideline.md 第5章</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>docs/guideline.md 第7章</t>
+          <t>docs/guideline.md 第5章</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>docs/guideline.md 第7章</t>
+          <t>docs/guideline.md 第5章</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>docs/guideline.md 第4章</t>
+          <t>docs/guideline.md 全体</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>docs/guideline.md 第4章</t>
+          <t>docs/guideline.md 第3章</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2693,7 +2693,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>docs/guideline.md 第4章</t>
+          <t>docs/guideline.md 第3章</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>docs/guideline.md 第4章</t>
+          <t>docs/guideline.md 第3章</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>docs/guideline.md 第9章</t>
+          <t>docs/guideline.md 第8章・第9章</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>docs/guideline.md 第9章</t>
+          <t>docs/guideline.md 第7章</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>docs/guideline.md 第10章</t>
+          <t>docs/guideline.md 第8章</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>docs/guideline.md 第8章</t>
+          <t>docs/guideline.md 第6章</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2965,27 +2965,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M001</t>
+          <t>L018</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>通知・資料</t>
+          <t>法令</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>公立学校施設の目的外使用に係る留意事項の周知について（通知）</t>
+          <t>地方自治法第238条の4第7項</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>文部科学省</t>
+          <t>国</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2024-12-24</t>
+          <t>1947-04-17</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2995,29 +2995,29 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.mext.go.jp/b_menu/hakusho/nc/mext_00095.html</t>
+          <t>https://laws.e-gov.go.jp/law/322AC0000000067</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>学校施設利用</t>
+          <t>行政財産の目的外使用</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>docs/guideline.md 第5章</t>
+          <t>docs/guideline.md 第2章</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>学校教育上の支障は物理的支障だけでなく教育的配慮や将来の支障も含み得るとの判例言及あり</t>
+          <t>文科省通知M001が学校教育法137条等と併記して説明。学校施設の当然利用ではなく許可・判断の問題として整理</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M002</t>
+          <t>M001</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3027,7 +3027,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>【資料3】学校・教師が担う業務に係る3分類 更なる役割分担・適正化の推進に向けた取組について</t>
+          <t>公立学校施設の目的外使用に係る留意事項の周知について（通知）</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2023-07-24</t>
+          <t>2024-12-24</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -3047,29 +3047,29 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.mext.go.jp/content/20230725-mext_zaimu-000031116_3.pdf</t>
+          <t>https://www.mext.go.jp/b_menu/hakusho/nc/mext_00095.html</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>教職員の業務適正化</t>
+          <t>学校施設利用</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>docs/guideline.md 第9章</t>
+          <t>docs/guideline.md 第2章</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>PTA本来事務を直接扱う資料ではないため学校業務見直しの補助根拠として使う</t>
+          <t>学校教育上の支障は物理的支障だけでなく教育的配慮や将来の支障も含み得るとの判例言及あり</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P001</t>
+          <t>M002</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>公立学校とPTAの間で個人情報のやり取りをするためのポイント</t>
+          <t>【資料3】学校・教師が担う業務に係る3分類 更なる役割分担・適正化の推進に向けた取組について</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>個人情報保護委員会事務局</t>
+          <t>文部科学省</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2023-07-24</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -3099,49 +3099,49 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.ppc.go.jp/files/pdf/202603_school_pta_pd_point.pdf</t>
+          <t>https://www.mext.go.jp/content/20230725-mext_zaimu-000031116_3.pdf</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>個人情報</t>
+          <t>教職員の業務適正化</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>docs/guideline.md 第7章</t>
+          <t>docs/guideline.md 第6章・第7章</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>本文・図解ともに中核資料。公立学校側とPTA側双方のポイントを扱う</t>
+          <t>PTA会費は学校徴収金ですらないため、PTA会費徴収への教職員関与を見直す補助根拠として使う</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C001</t>
+          <t>P001</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>行政資料</t>
+          <t>通知・資料</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>消費者契約法逐条解説 第2条（定義）</t>
+          <t>公立学校とPTAの間で個人情報のやり取りをするためのポイント</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>消費者庁</t>
+          <t>個人情報保護委員会事務局</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2023-09</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -3151,96 +3151,96 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.caa.go.jp/policies/policy/consumer_system/consumer_contract_act/annotations/assets/consumer_system_cms203_230915_04.pdf</t>
+          <t>https://www.ppc.go.jp/files/pdf/202603_school_pta_pd_point.pdf</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>消費者契約法</t>
+          <t>個人情報</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>docs/guideline.md 第4章</t>
+          <t>docs/guideline.md 第5章</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>PTA入会に消費者契約法を使う場合は直接適用の断定を避け契約環境・誤認・心理的圧迫の説明に使う</t>
+          <t>本文・図解ともに中核資料。公立学校側とPTA側双方のポイントを扱う</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Y001</t>
+          <t>C001</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>自治体通知</t>
+          <t>行政資料</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>横浜市教育委員会通知 学教第1965号</t>
+          <t>消費者契約法逐条解説 第2条（定義）</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>横浜市教育委員会</t>
+          <t>消費者庁</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>2023-09</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>https://www.caa.go.jp/policies/policy/consumer_system/consumer_contract_act/annotations/assets/consumer_system_cms203_230915_04.pdf</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>任意加入・学校徴収金分離・名簿提供</t>
+          <t>消費者契約法</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>docs/guideline.md 全体</t>
+          <t>docs/guideline.md 第3章</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>ユーザー保有資料から正式情報を確認する。公開URL又は文書画像が必要</t>
+          <t>PTA入会に消費者契約法を使う場合は直接適用の断定を避け契約環境・誤認・心理的圧迫の説明に使う</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A001</t>
+          <t>Y001</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>自治体回答</t>
+          <t>自治体通知</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>仙台市教育委員会回答</t>
+          <t>横浜市教育委員会通知 学教第1965号</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>仙台市教育委員会</t>
+          <t>横浜市教育委員会</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -3260,67 +3260,119 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>入会意思確認・会費徴収・名簿提供</t>
+          <t>任意加入・学校徴収金分離・名簿提供</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>docs/guideline.md 参考資料</t>
+          <t>docs/guideline.md 全体</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>ユーザー保有メール・回答本文から確認する</t>
+          <t>ユーザー保有資料から正式情報を確認する。公開URL又は文書画像が必要</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>A001</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>自治体回答</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>仙台市教育委員会回答</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>仙台市教育委員会</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>入会意思確認・会費徴収・名簿提供</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>docs/guideline.md 参考資料</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>ユーザー保有メール・回答本文から確認する</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>A002</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>自治体回答</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>広島市教育委員会回答</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>広島市教育委員会</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>職務専念義務免除・PTA事務</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>docs/guideline.md 第9章</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>docs/guideline.md 第7章</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
         <is>
           <t>回答本文から正確に反映する</t>
         </is>

--- a/public/xlsx/pta-school-separation-school-survey.xlsx
+++ b/public/xlsx/pta-school-separation-school-survey.xlsx
@@ -305,12 +305,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>入会前に役員希望調査・委員希望調査・免除申請を配布又は回収していないか</t>
+          <t>入会同意・名簿提供同意・会費徴収同意が別個の意思表示として分かれているか</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>していない／している／要確認</t>
+          <t>分離済み／一体化／要確認</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -340,22 +340,22 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>L001・L010・L012</t>
+          <t>L001・L007・L008・L010・P001</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>加入前提の心理的圧迫が生じる</t>
+          <t>保護者が何に同意したか不明確になり自由な同意が疑われる</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>役員希望調査等は加入確認後の会員だけに限定する</t>
+          <t>入会・名簿提供・会費徴収を別項目として説明し同意を分ける</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>役員希望調査票・免除申請書・年度当初配布資料</t>
+          <t>入会申込書・同意書・口座振替依頼書</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -377,12 +377,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>PTAに加入しないことにより児童生徒又は保護者に不利益を生じさせないことを明示しているか</t>
+          <t>入会前に役員希望調査・委員希望調査・免除申請を配布又は回収していないか</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>明示あり／明示なし／要確認</t>
+          <t>していない／している／要確認</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -412,22 +412,22 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>L010・L011・L012</t>
+          <t>L001・L010・L012</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>非加入選択が事実上困難になる</t>
+          <t>加入前提の心理的圧迫が生じる</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>加入案内に非加入不利益なしを明記する</t>
+          <t>役員希望調査等は加入確認後の会員だけに限定する</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>加入案内・FAQ・説明会資料</t>
+          <t>役員希望調査票・免除申請書・年度当初配布資料</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -444,17 +444,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>役員選出</t>
+          <t>入会</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>入会申込記録が確認できない保護者を役員選出対象にしていないか</t>
+          <t>PTAに加入しないことにより児童生徒又は保護者に不利益を生じさせないことを明示しているか</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>していない／している／要確認</t>
+          <t>明示あり／明示なし／要確認</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -484,22 +484,22 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>L001・L002</t>
+          <t>L010・L011・L012</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>強制加入・強制役務の疑いが生じる</t>
+          <t>非加入選択が事実上困難になる</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>役員選出対象を加入確認済み会員に限定する</t>
+          <t>加入案内に非加入不利益なしを明記する</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>役員選出規定・抽選名簿作成方法の説明</t>
+          <t>加入案内・FAQ・説明会資料</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -521,7 +521,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>くじ引き・抽選・免除審査を学校施設内又は学校行事直後に実施していないか</t>
+          <t>入会申込記録が確認できない保護者を役員選出対象にしていないか</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -556,22 +556,22 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>L003・M001・L010・L012</t>
+          <t>L001・L002</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>学校行事との混同により任意加入性が損なわれる</t>
+          <t>強制加入・強制役務の疑いが生じる</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>入会意思確認後にPTA主催手続として分離実施する</t>
+          <t>役員選出対象を加入確認済み会員に限定する</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>役員選出案内・実施日時・会場資料</t>
+          <t>役員選出規定・抽選名簿作成方法の説明</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -588,17 +588,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>会費徴収</t>
+          <t>役員選出</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>PTA会費を学校徴収金と同一通知・同一口座・同一引落しで処理していないか</t>
+          <t>くじ引き・抽選・免除審査を学校施設内又は学校行事直後に実施していないか</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>分離済み／混在／要確認</t>
+          <t>していない／している／要確認</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -628,22 +628,22 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>L001・L010・L017</t>
+          <t>L003・L018・M001・L010・L012</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>学校に支払うべき費用との誤認が生じる</t>
+          <t>学校行事との混同により任意加入性が損なわれる</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>PTA会費を学校徴収金から分離しPTA名義で徴収する</t>
+          <t>入会意思確認後にPTA主催手続として分離実施する</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>徴収通知・口座振替依頼書・会計処理説明</t>
+          <t>役員選出案内・実施日時・会場資料</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -665,12 +665,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>入会申込記録が確認できない保護者からPTA会費を徴収していないか</t>
+          <t>PTA会費を学校徴収金と同一通知・同一口座・同一引落しで処理していないか</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>していない／している／要確認</t>
+          <t>分離済み／混在／要確認</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -700,22 +700,22 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>L001</t>
+          <t>L001・L010・L017・M002</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>会費請求の根拠を欠き返還請求等のリスクがある</t>
+          <t>学校に支払うべき費用との誤認が生じる</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>加入確認ができない者への請求・徴収を停止する</t>
+          <t>PTA会費を学校徴収金から分離しPTA名義で徴収する</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>会員管理方法・会費請求対象の抽出方法</t>
+          <t>徴収通知・口座振替依頼書・会計処理説明</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>学校職員がPTA会費の徴収・督促・会計処理・名簿管理を行っていないか</t>
+          <t>入会申込記録が確認できない保護者からPTA会費を徴収していないか</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>行っていない／行っている／要確認</t>
+          <t>していない／している／要確認</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -772,22 +772,22 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>L015・M002</t>
+          <t>L001</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>職務専念義務・利益供与・事務負担未請求の問題が生じる</t>
+          <t>会費請求の根拠を欠き返還請求等のリスクがある</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>PTA会費事務をPTAに移管し学校関与を連絡調整に限定する</t>
+          <t>加入確認ができない者への請求・徴収を停止する</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>事務分掌・会計処理手順・職員作業内容</t>
+          <t>会員管理方法・会費請求対象の抽出方法</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -804,17 +804,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>個人情報</t>
+          <t>会費徴収</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>学校名簿をPTAの会員管理・役員選出・会費徴収に利用していないか</t>
+          <t>学校職員がPTA会費の徴収・督促・会計処理・名簿管理を行っていないか</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>利用なし／利用あり／要確認</t>
+          <t>行っていない／行っている／要確認</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -844,22 +844,22 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>L006・L008・P001</t>
+          <t>L015・M002</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>目的外利用・第三者提供の問題が生じる</t>
+          <t>職務専念義務・利益供与・事務負担未請求の問題が生じる</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>学校保有個人情報とPTA会員情報を分離する</t>
+          <t>PTA会費事務をPTAに移管し学校関与を連絡調整に限定する</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>名簿提供記録・利用目的説明・同意書様式</t>
+          <t>事務分掌・会計処理手順・職員作業内容</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -876,17 +876,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>個人情報</t>
+          <t>会費徴収</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>PTAへの個人情報提供について利用目的・提供範囲・本人同意・管理責任を説明しているか</t>
+          <t>PTA会費事務を学校が担っている場合に事務負担分の費用負担又は委託関係を文書化しているか</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>説明あり／説明なし／形式のみ</t>
+          <t>文書あり／文書なし／該当なし／要確認</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -916,22 +916,22 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>L007・L008・L009・P001</t>
+          <t>L015・L017・M002</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>自由な同意が認められないおそれがある</t>
+          <t>公的労務の無償提供・利益供与的問題が生じ得る</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>入会同意と名簿提供同意を分けて説明する</t>
+          <t>学校がPTA本来事務を担う運用を見直し必要な分離又は費用整理を行う</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>同意書・個人情報取扱説明・提供記録</t>
+          <t>委託契約・協定書・費用負担資料</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -953,12 +953,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>非会員又は未加入者の情報をPTAが把握できる状態になっていないか</t>
+          <t>学校名簿をPTAの会員管理・役員選出・会費徴収に利用していないか</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>なっていない／なっている／要確認</t>
+          <t>利用なし／利用あり／要確認</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -988,22 +988,22 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>L008・P001</t>
+          <t>L006・L008・P001</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>非会員特定のために学校情報へ依存する危険がある</t>
+          <t>目的外利用・第三者提供の問題が生じる</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>非会員情報をPTAに渡さない運用へ改める</t>
+          <t>学校保有個人情報とPTA会員情報を分離する</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>名簿項目・アクセス権限・連絡対象者抽出方法</t>
+          <t>名簿提供記録・利用目的説明・同意書様式</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1020,17 +1020,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>連絡ツール</t>
+          <t>個人情報</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>学校連絡ツールでPTA加入・会費・役員選出・免除申請等を送信していないか</t>
+          <t>PTAへの個人情報提供について利用目的・提供範囲・本人同意・管理責任を説明しているか</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>送信なし／送信あり／要確認</t>
+          <t>説明あり／説明なし／形式のみ</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1060,22 +1060,22 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>L008・L010・L012・P001</t>
+          <t>L007・L008・L009・P001</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>学校手続との誤認・目的外利用の問題が生じる</t>
+          <t>自由な同意が認められないおそれがある</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>PTA内部連絡はPTA独自手段に分離する</t>
+          <t>入会同意と名簿提供同意を分けて説明する</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>送信文面・送信主体・配信対象の説明</t>
+          <t>同意書・個人情報取扱説明・提供記録</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1092,17 +1092,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>配布回収</t>
+          <t>個人情報</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>児童経由でPTA加入申込・会費・免除書類・診断書等を回収していないか</t>
+          <t>同意しない保護者又は非会員の情報を削除又はマスキングする方法を定めているか</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>回収なし／回収あり／要確認</t>
+          <t>定めあり／定めなし／要確認</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1132,22 +1132,22 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>L008・L010・P001</t>
+          <t>L008・L009・P001</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>児童を介した心理的圧迫・個人情報管理リスクが生じる</t>
+          <t>不同意者情報がPTAに提供される危険がある</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>児童経由回収を停止しPTA独自手続に切り替える</t>
+          <t>不同意者情報を除外できない場合は学校名簿提供を行わない</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>配布回収方法・提出書類一覧</t>
+          <t>削除・マスキング手順・名簿項目・アクセス権限</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1164,17 +1164,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>入学式</t>
+          <t>個人情報</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>入学式又は学校説明会の直後にPTA加入・役員選出・くじ引きを実施していないか</t>
+          <t>非会員又は未加入者の情報をPTAが把握できる状態になっていないか</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>実施なし／実施あり／要確認</t>
+          <t>なっていない／なっている／要確認</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1204,22 +1204,22 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>L003・M001・L010・L012</t>
+          <t>L008・P001</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>学校行事との混同により任意加入性が損なわれる</t>
+          <t>非会員特定のために学校情報へ依存する危険がある</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>入学式本体とPTA手続を時間・資料・説明者で分離する</t>
+          <t>非会員情報をPTAに渡さない運用へ改める</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>入学式次第・説明会資料・PTA説明時間割</t>
+          <t>名簿項目・アクセス権限・連絡対象者抽出方法</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1236,17 +1236,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>学校施設</t>
+          <t>連絡ツール</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PTAの学校施設利用について目的外使用として確認しているか</t>
+          <t>学校連絡ツールでPTA加入・会費・役員選出・免除申請等を送信していないか</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>確認あり／確認なし／要確認</t>
+          <t>送信なし／送信あり／要確認</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1276,22 +1276,22 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>L003・M001</t>
+          <t>L008・L010・L012・P001</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>施設利用が当然視され学校運営との混同が生じる</t>
+          <t>学校手続との誤認・目的外利用の問題が生じる</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>施設利用許可時に任意加入・個人情報・会費徴収の適正性を確認する</t>
+          <t>PTA内部連絡はPTA独自手段に分離する</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>施設使用許可手続・許可条件・使用記録</t>
+          <t>送信文面・送信主体・配信対象の説明</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1308,17 +1308,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>学校施設</t>
+          <t>配布回収</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PTAの施設利用許可に任意加入・個人情報・会費徴収の適正性確認を条件としているか</t>
+          <t>児童経由でPTA加入申込・会費・免除書類・診断書等を回収していないか</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>条件あり／条件なし／要確認</t>
+          <t>回収なし／回収あり／要確認</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1348,22 +1348,22 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>L003・M001・P001</t>
+          <t>L008・L010・P001</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>不適切運用を学校施設が支える構造が残る</t>
+          <t>児童を介した心理的圧迫・個人情報管理リスクが生じる</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>改善確認まで施設利用又は学校関与を制限する</t>
+          <t>児童経由回収を停止しPTA独自手続に切り替える</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>施設利用許可条件・PTAとの確認文書</t>
+          <t>配布回収方法・提出書類一覧</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1380,17 +1380,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>教職員関与</t>
+          <t>入学式</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>教職員がPTA入会管理・会費徴収・会計・役員選出・免除審査を担っていないか</t>
+          <t>入学式又は学校説明会の直後にPTA加入・役員選出・くじ引きを実施していないか</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>担っていない／担っている／要確認</t>
+          <t>実施なし／実施あり／要確認</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1420,22 +1420,22 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>L015・M002</t>
+          <t>L003・L018・M001・L010・L012</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>職務専念義務・働き方改革との衝突が生じる</t>
+          <t>学校行事との混同により任意加入性が損なわれる</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>学校関与を連絡調整に限定する</t>
+          <t>入学式本体とPTA手続を時間・資料・説明者で分離する</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>事務分掌・PTA事務内容一覧・職専免関係資料</t>
+          <t>入学式次第・説明会資料・PTA説明時間割</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1452,17 +1452,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>教職員関与</t>
+          <t>学校施設</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>PTA事務に職務専念義務免除又は兼職兼業許可等を用いている場合その根拠文書があるか</t>
+          <t>PTAの学校施設利用について目的外使用として確認しているか</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>あり／なし／該当なし／要確認</t>
+          <t>確認あり／確認なし／要確認</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1492,22 +1492,22 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>L015・L016</t>
+          <t>L003・L018・M001</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>私的団体事務を公務化している疑義が生じる</t>
+          <t>施設利用が当然視され学校運営との混同が生じる</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>根拠・範囲・時間・対象事務を確認し本来事務をPTAに戻す</t>
+          <t>施設利用許可時に任意加入・個人情報・会費徴収の適正性を確認する</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>職専免承認記録・規則・要綱・運用通知</t>
+          <t>施設使用許可手続・許可条件・使用記録</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1524,17 +1524,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>管理職兼任</t>
+          <t>学校施設</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>校長・副校長・教頭がPTA副会長・会計・監査等にあて職で入っていないか</t>
+          <t>PTAの施設利用許可に任意加入・入会申込記録・個人情報・会費徴収の適正性確認を条件としているか</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>入っていない／入っている／要確認</t>
+          <t>条件あり／条件なし／要確認</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1564,22 +1564,22 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>L003・L004・L005・L015・L016</t>
+          <t>L003・L018・M001・P001</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>利益相反・監視機能欠如・社会教育法12条との矛盾が生じる</t>
+          <t>不適切運用を学校施設が支える構造が残る</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>学校管理職のPTA役員兼任を見直す</t>
+          <t>改善確認まで施設利用又は学校関与を制限する</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>PTA規約・役員名簿・職務分担表</t>
+          <t>施設利用許可条件・PTAとの確認文書</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1596,17 +1596,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>通知整備</t>
+          <t>学校施設</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>教育委員会が全校向けにPTA任意加入と分離原則を通知しているか</t>
+          <t>学校施設内でPTA説明会・役員選出・会費徴収を行う際に学校手続との混同防止措置を取っているか</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>通知済み／未通知／要確認</t>
+          <t>措置あり／措置なし／要確認</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1636,22 +1636,22 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>L001・L003・L005・L008・L015</t>
+          <t>L003・L018・M001・L010</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>学校ごとの慣行が放置される</t>
+          <t>学校が任意団体手続を主催しているとの誤認が生じる</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>全校通知と実態調査を実施する</t>
+          <t>時間・場所・説明者・資料を分離しPTA主催であることを明示する</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>教育委員会通知・校長会資料</t>
+          <t>会場案内・説明資料・実施記録</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1668,17 +1668,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>実態調査</t>
+          <t>教職員関与</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>教育委員会が各校PTAの入会申込記録・会費徴収・名簿利用の実態を把握しているか</t>
+          <t>教職員がPTA入会管理・会費徴収・会計・役員選出・免除審査を担っていないか</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>把握済み／未把握／要確認</t>
+          <t>担っていない／担っている／要確認</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>P001・M001</t>
+          <t>L015・M002</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>問題の有無を教育委員会が把握できない</t>
+          <t>職務専念義務・働き方改革との衝突が生じる</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>全校調査票を作成し報告を求める</t>
+          <t>学校関与を連絡調整に限定する</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>全校調査結果・学校別回答一覧</t>
+          <t>事務分掌・PTA事務内容一覧・職専免関係資料</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -1740,17 +1740,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>是正措置</t>
+          <t>教職員関与</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>問題が確認された学校について施設利用・連絡ツール利用・学校徴収金処理等を見直しているか</t>
+          <t>PTA事務に職務専念義務免除又は兼職兼業許可等を用いている場合その根拠文書があるか</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>見直し済み／未対応／要確認</t>
+          <t>あり／なし／該当なし／要確認</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1780,22 +1780,22 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>L003・L008・L015・M001・P001</t>
+          <t>L015・L016</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>違法・不適切運用が継続する</t>
+          <t>私的団体事務を公務化している疑義が生じる</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>改善完了まで学校関与を停止又は制限する</t>
+          <t>根拠・範囲・時間・対象事務を確認し本来事務をPTAに戻す</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>改善計画・学校への指導記録・PTAとの協議記録</t>
+          <t>職専免承認記録・規則・要綱・運用通知</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -1812,17 +1812,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>資料保存</t>
+          <t>教職員関与</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>入会申込記録・同意書・会費徴収資料・名簿提供記録の保存年限と管理責任を定めているか</t>
+          <t>学校がPTAに関与する範囲を連絡調整に限定しているか</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>定めあり／定めなし／要確認</t>
+          <t>限定済み／本来事務に関与／要確認</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1852,22 +1852,22 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>L001・L008・P001</t>
+          <t>L015・M002</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>後日検証ができず責任所在が不明確になる</t>
+          <t>任意団体事務が学校職務に吸収される</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>PTAと学校の保管資料を分け保存年限と管理責任を明確化する</t>
+          <t>入会・会費・名簿・役員・会計はPTAに戻し学校は連絡調整に限定する</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>保存規程・管理台帳・廃棄ルール</t>
+          <t>事務分掌・PTAとの役割分担表・校務分掌</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -1884,65 +1884,497 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
+          <t>管理職兼任</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>校長・副校長・教頭がPTA副会長・会計・監査等にあて職で入っていないか</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>入っていない／入っている／要確認</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>L003・L004・L005・L015・L016・L018</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>利益相反・監視機能欠如・社会教育法12条との矛盾が生じる</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>学校管理職のPTA役員兼任を見直す</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>PTA規約・役員名簿・職務分担表</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Q26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>管理職兼任</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>施設利用・個人情報提供・会費徴収を判断する学校管理職がPTA側役員を兼ねていないか</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>兼ねていない／兼ねている／要確認</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>L003・L005・L008・L018・P001</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>管理する側と利用する側の責任分界が曖昧になる</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>施設管理・個人情報管理・会計関与とPTA役員を分離する</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>PTA役員名簿・施設利用許可者・個人情報管理責任者一覧</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Q27</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>通知整備</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>教育委員会が全校向けにPTA任意加入と学校関与の分離原則を通知しているか</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>通知済み／未通知／要確認</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>L001・L003・L005・L008・L015</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>学校ごとの慣行が放置される</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>全校通知と実態調査を実施する</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>教育委員会通知・校長会資料</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Q28</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>実態調査</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>教育委員会が各校PTAの入会申込記録・会費徴収・名簿利用・施設利用・教職員関与の実態を把握しているか</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>把握済み／未把握／要確認</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>L001・L003・L008・L015・M001・P001</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>問題の有無を教育委員会が把握できない</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>全校調査票を作成し報告を求める</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>全校調査結果・学校別回答一覧</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Q29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>是正措置</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>問題が確認された学校について施設利用・連絡ツール利用・学校徴収金処理等を見直しているか</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>見直し済み／未対応／要確認</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>L003・L008・L015・L018・M001・P001</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>違法・不適切運用が継続する</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>改善完了まで学校関与を停止又は制限する</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>改善計画・学校への指導記録・PTAとの協議記録</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Q30</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>資料保存</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>入会申込記録・同意書・会費徴収資料・名簿提供記録の保存年限と管理責任を定めているか</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>定めあり／定めなし／要確認</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>L001・L008・P001</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>後日検証ができず責任所在が不明確になる</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>PTAと学校の保管資料を分け保存年限と管理責任を明確化する</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>保存規程・管理台帳・廃棄ルール</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Q31</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
           <t>保護者説明</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>保護者に対し学校とPTAが別主体であることを説明するFAQ又は案内を用意しているか</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>あり／なし／要確認</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
+      <c r="E32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
         <is>
           <t>L010・L011・P001</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>誤認や苦情が繰り返される</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>任意加入・非加入不利益なし・個人情報・会費分離を説明する資料を整備する</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>FAQ・保護者向け案内・説明会資料</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t/>
         </is>

--- a/public/xlsx/pta-school-separation-school-survey.xlsx
+++ b/public/xlsx/pta-school-separation-school-survey.xlsx
@@ -2454,8 +2454,9 @@
     <col min="6" max="6" width="14" customWidth="1"/>
     <col min="7" max="7" width="46" customWidth="1"/>
     <col min="8" max="8" width="24" customWidth="1"/>
-    <col min="9" max="9" width="24" customWidth="1"/>
-    <col min="10" max="10" width="42" customWidth="1"/>
+    <col min="9" max="9" width="42" customWidth="1"/>
+    <col min="10" max="10" width="24" customWidth="1"/>
+    <col min="11" max="11" width="42" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2501,10 +2502,15 @@
       </c>
       <c r="I1" t="inlineStr" s="1">
         <is>
+          <t>引用箇所</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr" s="1">
+        <is>
           <t>掲載先</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr" s="1">
+      <c r="K1" t="inlineStr" s="1">
         <is>
           <t>備考</t>
         </is>
@@ -2553,10 +2559,15 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>契約の成立には申込みと承諾が必要である旨</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>docs/guideline.md 第3章</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>e-Gov法令検索で法令ページ確認済み。条文本文の正確な引用は次段階で条文単位確認</t>
         </is>
@@ -2605,10 +2616,15 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>代理権を有しない者がした契約は本人の追認がなければ本人に効力を生じない旨</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>docs/guideline.md 第3章</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>無限代理ではなく無権代理として整理。条文本文の正確な引用は次段階で条文単位確認</t>
         </is>
@@ -2657,10 +2673,15 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>学校教育上支障のない限り学校施設を社会教育その他公共のために利用させることができる旨</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>docs/guideline.md 第2章</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>地方自治法238条の4第7項及び文科省通知M001と併用。目的外使用は当然利用ではないことを説明</t>
         </is>
@@ -2709,10 +2730,15 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>社会教育関係団体の定義</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>docs/guideline.md 第9章</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>PTAの一般的位置付けとして使用。条文本文の正確な引用は次段階で確認</t>
         </is>
@@ -2761,10 +2787,15 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>国及び地方公共団体による不当な統制的支配又は事業干渉の禁止</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>docs/guideline.md 第8章・第10章</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>責任回避条文ではなく学校混在の是正根拠として整理</t>
         </is>
@@ -2813,10 +2844,15 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>行政機関等が法令の定める所掌事務又は業務の範囲内で利用目的をできる限り特定して保有する規律</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>docs/guideline.md 第5章</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>PPC資料P001が61条の使い方を学校・PTA文脈で説明</t>
         </is>
@@ -2865,10 +2901,15 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>本人から直接書面等で取得するときの利用目的明示</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>docs/guideline.md 第5章</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>PPC資料P001が学校保護者への説明文脈で言及</t>
         </is>
@@ -2917,10 +2958,15 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>保有個人情報の利用及び提供の制限</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>docs/guideline.md 第5章</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>学校からPTAへの提供問題の中心。PPC資料P001と併用</t>
         </is>
@@ -2969,10 +3015,15 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>提供先に対する制限又は措置要求</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>docs/guideline.md 第5章</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>PPC資料P001が単なる提供の場合の措置要求として説明</t>
         </is>
@@ -3021,10 +3072,15 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>消費者と事業者の情報及び交渉力の格差への配慮</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>docs/guideline.md 全体</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>PTA入会手続の心理的圧迫の説明に使用</t>
         </is>
@@ -3073,10 +3129,15 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>契約条項等の明確化・情報提供</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>docs/guideline.md 第3章</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>PTAの案内文・加入手続の説明に使用</t>
         </is>
@@ -3125,10 +3186,15 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
+          <t>不実告知・不利益事実の不告知等</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
           <t>docs/guideline.md 第3章</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>学校手続との混在による誤認の説明に使用。適用可否は個別判断として書く</t>
         </is>
@@ -3177,10 +3243,15 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
+          <t>消費者の利益を一方的に害する条項</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>docs/guideline.md 第3章</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>自動加入・退会制限等の検討用。適用可否は個別判断として書く</t>
         </is>
@@ -3229,10 +3300,15 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
+          <t>職員の秘密を守る義務</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
           <t>docs/guideline.md 第8章・第9章</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>名簿提供・漏えいリスクとの関係で必要に応じて使用</t>
         </is>
@@ -3281,10 +3357,15 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
+          <t>勤務時間及び職務上の注意力を職責遂行に用いる義務</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
           <t>docs/guideline.md 第7章</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>教職員のPTA本来事務従事の中心論点</t>
         </is>
@@ -3333,10 +3414,15 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
+          <t>兼職・兼業関係の確認対象</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
           <t>docs/guideline.md 第8章</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>第37条ではなく第38条側を確認。PTA役員兼任は35条・服務・利益相反と併せて整理</t>
         </is>
@@ -3385,10 +3471,15 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
+          <t>住民への寄附金等の割当的徴収禁止</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
           <t>docs/guideline.md 第6章</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>PTA会費と学校徴収金混在の説明に使用。PTA会費そのものとの関係は慎重に書く</t>
         </is>
@@ -3437,10 +3528,15 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
+          <t>行政財産は用途又は目的を妨げない限度で使用許可できる旨</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
           <t>docs/guideline.md 第2章</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>文科省通知M001が学校教育法137条等と併記して説明。学校施設の当然利用ではなく許可・判断の問題として整理</t>
         </is>
@@ -3489,10 +3585,15 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
+          <t>地方自治法238条の4第7項と学校教育法137条等を踏まえ学校教育上支障のない限り目的外使用可能と説明</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
           <t>docs/guideline.md 第2章</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>学校教育上の支障は物理的支障だけでなく教育的配慮や将来の支障も含み得るとの判例言及あり</t>
         </is>
@@ -3541,10 +3642,15 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
+          <t>学校徴収金の徴収・管理について学校以外が担うべき業務として各教育委員会の権限と責任において取組を進める考え方を示す</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
           <t>docs/guideline.md 第6章・第7章</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>PTA会費は学校徴収金ですらないため、PTA会費徴収への教職員関与を見直す補助根拠として使う</t>
         </is>
@@ -3593,10 +3699,15 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
+          <t>公立学校とPTAの個人情報のやり取りにおける利用目的・目的外提供・本人同意・委託/単なる提供・PTA側の個人情報取扱事業者該当性</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
           <t>docs/guideline.md 第5章</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>本文・図解ともに中核資料。公立学校側とPTA側双方のポイントを扱う</t>
         </is>
@@ -3645,10 +3756,15 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
+          <t>情報・交渉力格差、事業者概念、その他の団体にPTAが含まれる旨</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
           <t>docs/guideline.md 第3章</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>PTA入会に消費者契約法を使う場合は直接適用の断定を避け契約環境・誤認・心理的圧迫の説明に使う</t>
         </is>
@@ -3697,10 +3813,15 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
+          <t>PTA任意加入・加入届・会費分離・個人情報の整理</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
           <t>docs/guideline.md 全体</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>ユーザー保有資料から正式情報を確認する。公開URL又は文書画像が必要</t>
         </is>
@@ -3749,10 +3870,15 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
+          <t>自治体回答例として使用予定</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
           <t>docs/guideline.md 参考資料</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>ユーザー保有メール・回答本文から確認する</t>
         </is>
@@ -3801,10 +3927,15 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
+          <t>職専免の根拠説明例として使用予定</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
           <t>docs/guideline.md 第7章</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>回答本文から正確に反映する</t>
         </is>

--- a/public/xlsx/pta-school-separation-school-survey.xlsx
+++ b/public/xlsx/pta-school-separation-school-survey.xlsx
@@ -2519,7 +2519,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>L001</t>
+          <t>L019</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>民法第522条</t>
+          <t>民法第521条</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -2554,12 +2554,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>入会契約</t>
+          <t>契約自由</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>契約の成立には申込みと承諾が必要である旨</t>
+          <t>契約の締結及び内容は法令の制限内で当事者が自由に決定できる旨</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -2576,7 +2576,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L002</t>
+          <t>L001</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>民法第113条</t>
+          <t>民法第522条</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>無権代理</t>
+          <t>入会契約</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>代理権を有しない者がした契約は本人の追認がなければ本人に効力を生じない旨</t>
+          <t>契約の成立には申込みと承諾が必要である旨</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -2626,14 +2626,14 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>無限代理ではなく無権代理として整理。条文本文の正確な引用は次段階で条文単位確認</t>
+          <t>e-Gov法令検索で法令ページ確認済み。条文本文の正確な引用は次段階で条文単位確認</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L003</t>
+          <t>L002</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>学校教育法第137条</t>
+          <t>民法第113条</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2653,7 +2653,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1947-03-31</t>
+          <t>1896-04-27</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -2663,34 +2663,34 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://laws.e-gov.go.jp/law/322AC0000000026</t>
+          <t>https://laws.e-gov.go.jp/law/129AC0000000089</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>学校施設目的外使用</t>
+          <t>無権代理</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>学校教育上支障のない限り学校施設を社会教育その他公共のために利用させることができる旨</t>
+          <t>代理権を有しない者がした契約は本人の追認がなければ本人に効力を生じない旨</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>docs/guideline.md 第2章</t>
+          <t>docs/guideline.md 第3章</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>地方自治法238条の4第7項及び文科省通知M001と併用。目的外使用は当然利用ではないことを説明</t>
+          <t>無限代理ではなく無権代理として整理。条文本文の正確な引用は次段階で条文単位確認</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L004</t>
+          <t>L003</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>社会教育法第10条</t>
+          <t>学校教育法第137条</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1949-06-10</t>
+          <t>1947-03-31</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -2720,34 +2720,34 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://laws.e-gov.go.jp/law/324AC0000000207</t>
+          <t>https://laws.e-gov.go.jp/law/322AC0000000026</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>社会教育関係団体</t>
+          <t>学校施設目的外使用</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>社会教育関係団体の定義</t>
+          <t>学校教育上支障のない限り学校施設を社会教育その他公共のために利用させることができる旨</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>docs/guideline.md 第9章</t>
+          <t>docs/guideline.md 第2章</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>PTAの一般的位置付けとして使用。条文本文の正確な引用は次段階で確認</t>
+          <t>地方自治法238条の4第7項及び文科省通知M001と併用。目的外使用は当然利用ではないことを説明</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L005</t>
+          <t>L004</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>社会教育法第12条</t>
+          <t>社会教育法第10条</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2782,29 +2782,29 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>統制的支配干渉の禁止</t>
+          <t>社会教育関係団体</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>国及び地方公共団体による不当な統制的支配又は事業干渉の禁止</t>
+          <t>社会教育関係団体の定義</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>docs/guideline.md 第8章・第10章</t>
+          <t>docs/guideline.md 第9章</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>責任回避条文ではなく学校混在の是正根拠として整理</t>
+          <t>PTAの一般的位置付けとして使用。条文本文の正確な引用は次段階で確認</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L006</t>
+          <t>L005</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>個人情報保護法第61条</t>
+          <t>社会教育法第12条</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2003-05-30</t>
+          <t>1949-06-10</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2834,34 +2834,34 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://laws.e-gov.go.jp/law/415AC0000000057</t>
+          <t>https://laws.e-gov.go.jp/law/324AC0000000207</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>保有個人情報</t>
+          <t>統制的支配干渉の禁止</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>行政機関等が法令の定める所掌事務又は業務の範囲内で利用目的をできる限り特定して保有する規律</t>
+          <t>国及び地方公共団体による不当な統制的支配又は事業干渉の禁止</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>docs/guideline.md 第5章</t>
+          <t>docs/guideline.md 第8章・第10章</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>PPC資料P001が61条の使い方を学校・PTA文脈で説明</t>
+          <t>責任回避条文ではなく学校混在の是正根拠として整理</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L007</t>
+          <t>L006</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>個人情報保護法第62条</t>
+          <t>個人情報保護法第61条</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>利用目的明示</t>
+          <t>保有個人情報</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>本人から直接書面等で取得するときの利用目的明示</t>
+          <t>行政機関等が法令の定める所掌事務又は業務の範囲内で利用目的をできる限り特定して保有する規律</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -2911,14 +2911,14 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>PPC資料P001が学校保護者への説明文脈で言及</t>
+          <t>PPC資料P001が61条の使い方を学校・PTA文脈で説明</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L008</t>
+          <t>L007</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>個人情報保護法第69条</t>
+          <t>個人情報保護法第62条</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>目的外利用・提供</t>
+          <t>利用目的明示</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>保有個人情報の利用及び提供の制限</t>
+          <t>本人から直接書面等で取得するときの利用目的明示</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -2968,14 +2968,14 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>学校からPTAへの提供問題の中心。PPC資料P001と併用</t>
+          <t>PPC資料P001が学校保護者への説明文脈で言及</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L009</t>
+          <t>L008</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2985,7 +2985,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>個人情報保護法第70条</t>
+          <t>個人情報保護法第69条</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -3010,12 +3010,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>提供先への措置要求</t>
+          <t>目的外利用・提供</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>提供先に対する制限又は措置要求</t>
+          <t>保有個人情報の利用及び提供の制限</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -3025,14 +3025,14 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>PPC資料P001が単なる提供の場合の措置要求として説明</t>
+          <t>学校からPTAへの提供問題の中心。PPC資料P001と併用</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>L010</t>
+          <t>L009</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3042,7 +3042,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>消費者契約法第1条</t>
+          <t>個人情報保護法第70条</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2000-05-12</t>
+          <t>2003-05-30</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -3062,34 +3062,34 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://laws.e-gov.go.jp/law/412AC0000000061</t>
+          <t>https://laws.e-gov.go.jp/law/415AC0000000057</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>情報格差・交渉力格差</t>
+          <t>提供先への措置要求</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>消費者と事業者の情報及び交渉力の格差への配慮</t>
+          <t>提供先に対する制限又は措置要求</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>docs/guideline.md 全体</t>
+          <t>docs/guideline.md 第5章</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>PTA入会手続の心理的圧迫の説明に使用</t>
+          <t>PPC資料P001が単なる提供の場合の措置要求として説明</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>L011</t>
+          <t>L010</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>消費者契約法第3条</t>
+          <t>消費者契約法第1条</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -3124,29 +3124,29 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>事業者の努力義務</t>
+          <t>情報格差・交渉力格差</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>契約条項等の明確化・情報提供</t>
+          <t>消費者と事業者の情報及び交渉力の格差への配慮</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>docs/guideline.md 第3章</t>
+          <t>docs/guideline.md 全体</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>PTAの案内文・加入手続の説明に使用</t>
+          <t>PTA入会手続の心理的圧迫の説明に使用</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>L012</t>
+          <t>L011</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>消費者契約法第4条</t>
+          <t>消費者契約法第3条</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>誤認・困惑取消し</t>
+          <t>事業者の努力義務</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>不実告知・不利益事実の不告知等</t>
+          <t>契約条項等の明確化・情報提供</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -3196,14 +3196,14 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>学校手続との混在による誤認の説明に使用。適用可否は個別判断として書く</t>
+          <t>PTAの案内文・加入手続の説明に使用</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>L013</t>
+          <t>L012</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>消費者契約法第10条</t>
+          <t>消費者契約法第4条</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3238,12 +3238,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>不当条項</t>
+          <t>誤認・困惑取消し</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>消費者の利益を一方的に害する条項</t>
+          <t>不実告知・不利益事実の不告知等</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -3253,14 +3253,14 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>自動加入・退会制限等の検討用。適用可否は個別判断として書く</t>
+          <t>学校手続との混在による誤認の説明に使用。適用可否は個別判断として書く</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L014</t>
+          <t>L013</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>地方公務員法第34条</t>
+          <t>消費者契約法第10条</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1950-12-13</t>
+          <t>2000-05-12</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3290,34 +3290,34 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://laws.e-gov.go.jp/law/325AC0000000261</t>
+          <t>https://laws.e-gov.go.jp/law/412AC0000000061</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>守秘義務</t>
+          <t>不当条項</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>職員の秘密を守る義務</t>
+          <t>消費者の利益を一方的に害する条項</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>docs/guideline.md 第8章・第9章</t>
+          <t>docs/guideline.md 第3章</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>名簿提供・漏えいリスクとの関係で必要に応じて使用</t>
+          <t>自動加入・退会制限等の検討用。適用可否は個別判断として書く</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L015</t>
+          <t>L014</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3327,7 +3327,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>地方公務員法第35条</t>
+          <t>地方公務員法第34条</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3352,29 +3352,29 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>職務専念義務</t>
+          <t>守秘義務</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>勤務時間及び職務上の注意力を職責遂行に用いる義務</t>
+          <t>職員の秘密を守る義務</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>docs/guideline.md 第7章</t>
+          <t>docs/guideline.md 第8章・第9章</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>教職員のPTA本来事務従事の中心論点</t>
+          <t>名簿提供・漏えいリスクとの関係で必要に応じて使用</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L016</t>
+          <t>L015</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>地方公務員法第38条</t>
+          <t>地方公務員法第35条</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3409,29 +3409,29 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>営利企業従事等制限</t>
+          <t>職務専念義務</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>兼職・兼業関係の確認対象</t>
+          <t>勤務時間及び職務上の注意力を職責遂行に用いる義務</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>docs/guideline.md 第8章</t>
+          <t>docs/guideline.md 第7章</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>第37条ではなく第38条側を確認。PTA役員兼任は35条・服務・利益相反と併せて整理</t>
+          <t>教職員のPTA本来事務従事の中心論点</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L017</t>
+          <t>L016</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>地方財政法第4条の5</t>
+          <t>地方公務員法第38条</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1948-07-07</t>
+          <t>1950-12-13</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://laws.e-gov.go.jp/law/323AC0000000109</t>
+          <t>https://laws.e-gov.go.jp/law/325AC0000000261</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>割当的寄附の禁止</t>
+          <t>営利企業従事等制限</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>住民への寄附金等の割当的徴収禁止</t>
+          <t>兼職・兼業関係の確認対象</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>docs/guideline.md 第6章</t>
+          <t>docs/guideline.md 第8章</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>PTA会費と学校徴収金混在の説明に使用。PTA会費そのものとの関係は慎重に書く</t>
+          <t>第37条ではなく第38条側を確認。PTA役員兼任は35条・服務・利益相反と併せて整理</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L018</t>
+          <t>L017</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>地方自治法第238条の4第7項</t>
+          <t>地方財政法第4条の5</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1947-04-17</t>
+          <t>1948-07-07</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3518,54 +3518,54 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://laws.e-gov.go.jp/law/322AC0000000067</t>
+          <t>https://laws.e-gov.go.jp/law/323AC0000000109</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>行政財産の目的外使用</t>
+          <t>割当的寄附の禁止</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>行政財産は用途又は目的を妨げない限度で使用許可できる旨</t>
+          <t>住民への寄附金等の割当的徴収禁止</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>docs/guideline.md 第2章</t>
+          <t>docs/guideline.md 第6章</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>文科省通知M001が学校教育法137条等と併記して説明。学校施設の当然利用ではなく許可・判断の問題として整理</t>
+          <t>PTA会費と学校徴収金混在の説明に使用。PTA会費そのものとの関係は慎重に書く</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M001</t>
+          <t>L018</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>通知・資料</t>
+          <t>法令</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>公立学校施設の目的外使用に係る留意事項の周知について（通知）</t>
+          <t>地方自治法第238条の4第7項</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>文部科学省</t>
+          <t>国</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2024-12-24</t>
+          <t>1947-04-17</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -3575,17 +3575,17 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.mext.go.jp/b_menu/hakusho/nc/mext_00095.html</t>
+          <t>https://laws.e-gov.go.jp/law/322AC0000000067</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>学校施設利用</t>
+          <t>行政財産の目的外使用</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>地方自治法238条の4第7項と学校教育法137条等を踏まえ学校教育上支障のない限り目的外使用可能と説明</t>
+          <t>行政財産は用途又は目的を妨げない限度で使用許可できる旨</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3595,14 +3595,14 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>学校教育上の支障は物理的支障だけでなく教育的配慮や将来の支障も含み得るとの判例言及あり</t>
+          <t>文科省通知M001が学校教育法137条等と併記して説明。学校施設の当然利用ではなく許可・判断の問題として整理</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M002</t>
+          <t>M001</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>【資料3】学校・教師が担う業務に係る3分類 更なる役割分担・適正化の推進に向けた取組について</t>
+          <t>公立学校施設の目的外使用に係る留意事項の周知について（通知）</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2023-07-24</t>
+          <t>2024-12-24</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -3632,34 +3632,34 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.mext.go.jp/content/20230725-mext_zaimu-000031116_3.pdf</t>
+          <t>https://www.mext.go.jp/b_menu/hakusho/nc/mext_00095.html</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>教職員の業務適正化</t>
+          <t>学校施設利用</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>学校徴収金の徴収・管理について学校以外が担うべき業務として各教育委員会の権限と責任において取組を進める考え方を示す</t>
+          <t>地方自治法238条の4第7項と学校教育法137条等を踏まえ学校教育上支障のない限り目的外使用可能と説明</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>docs/guideline.md 第6章・第7章</t>
+          <t>docs/guideline.md 第2章</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>PTA会費は学校徴収金ですらないため、PTA会費徴収への教職員関与を見直す補助根拠として使う</t>
+          <t>学校教育上の支障は物理的支障だけでなく教育的配慮や将来の支障も含み得るとの判例言及あり</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P001</t>
+          <t>M002</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3669,17 +3669,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>公立学校とPTAの間で個人情報のやり取りをするためのポイント</t>
+          <t>【資料3】学校・教師が担う業務に係る3分類 更なる役割分担・適正化の推進に向けた取組について</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>個人情報保護委員会事務局</t>
+          <t>文部科学省</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2023-07-24</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -3689,54 +3689,54 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.ppc.go.jp/files/pdf/202603_school_pta_pd_point.pdf</t>
+          <t>https://www.mext.go.jp/content/20230725-mext_zaimu-000031116_3.pdf</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>個人情報</t>
+          <t>教職員の業務適正化</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>公立学校とPTAの個人情報のやり取りにおける利用目的・目的外提供・本人同意・委託/単なる提供・PTA側の個人情報取扱事業者該当性</t>
+          <t>学校徴収金の徴収・管理について学校以外が担うべき業務として各教育委員会の権限と責任において取組を進める考え方を示す</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>docs/guideline.md 第5章</t>
+          <t>docs/guideline.md 第6章・第7章</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>本文・図解ともに中核資料。公立学校側とPTA側双方のポイントを扱う</t>
+          <t>PTA会費は学校徴収金ですらないため、PTA会費徴収への教職員関与を見直す補助根拠として使う</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C001</t>
+          <t>P001</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>行政資料</t>
+          <t>通知・資料</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>消費者契約法逐条解説 第2条（定義）</t>
+          <t>公立学校とPTAの間で個人情報のやり取りをするためのポイント</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>消費者庁</t>
+          <t>個人情報保護委員会事務局</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2023-09</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -3746,106 +3746,106 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.caa.go.jp/policies/policy/consumer_system/consumer_contract_act/annotations/assets/consumer_system_cms203_230915_04.pdf</t>
+          <t>https://www.ppc.go.jp/files/pdf/202603_school_pta_pd_point.pdf</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>消費者契約法</t>
+          <t>個人情報</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>情報・交渉力格差、事業者概念、その他の団体にPTAが含まれる旨</t>
+          <t>公立学校とPTAの個人情報のやり取りにおける利用目的・目的外提供・本人同意・委託/単なる提供・PTA側の個人情報取扱事業者該当性</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>docs/guideline.md 第3章</t>
+          <t>docs/guideline.md 第5章</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>PTA入会に消費者契約法を使う場合は直接適用の断定を避け契約環境・誤認・心理的圧迫の説明に使う</t>
+          <t>本文・図解ともに中核資料。公立学校側とPTA側双方のポイントを扱う</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Y001</t>
+          <t>C001</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>自治体通知</t>
+          <t>行政資料</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>横浜市教育委員会通知 学教第1965号</t>
+          <t>消費者契約法逐条解説 第2条（定義）</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>横浜市教育委員会</t>
+          <t>消費者庁</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>2023-09</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>https://www.caa.go.jp/policies/policy/consumer_system/consumer_contract_act/annotations/assets/consumer_system_cms203_230915_04.pdf</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>任意加入・学校徴収金分離・名簿提供</t>
+          <t>消費者契約法</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>PTA任意加入・加入届・会費分離・個人情報の整理</t>
+          <t>情報・交渉力格差、事業者概念、その他の団体にPTAが含まれる旨</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>docs/guideline.md 全体</t>
+          <t>docs/guideline.md 第3章</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>ユーザー保有資料から正式情報を確認する。公開URL又は文書画像が必要</t>
+          <t>PTA入会に消費者契約法を使う場合は直接適用の断定を避け契約環境・誤認・心理的圧迫の説明に使う</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A001</t>
+          <t>Y001</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>自治体回答</t>
+          <t>自治体通知</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>仙台市教育委員会回答</t>
+          <t>横浜市教育委員会通知 学教第1965号</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>仙台市教育委員会</t>
+          <t>横浜市教育委員会</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -3865,77 +3865,134 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>入会意思確認・会費徴収・名簿提供</t>
+          <t>任意加入・学校徴収金分離・名簿提供</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>自治体回答例として使用予定</t>
+          <t>PTA任意加入・加入届・会費分離・個人情報の整理</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>docs/guideline.md 参考資料</t>
+          <t>docs/guideline.md 全体</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>ユーザー保有メール・回答本文から確認する</t>
+          <t>ユーザー保有資料から正式情報を確認する。公開URL又は文書画像が必要</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>A001</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>自治体回答</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>仙台市教育委員会回答</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>仙台市教育委員会</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>入会意思確認・会費徴収・名簿提供</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>自治体回答例として使用予定</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>docs/guideline.md 参考資料</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>ユーザー保有メール・回答本文から確認する</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>A002</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>自治体回答</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>広島市教育委員会回答</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>広島市教育委員会</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>職務専念義務免除・PTA事務</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>職専免の根拠説明例として使用予定</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>docs/guideline.md 第7章</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>回答本文から正確に反映する</t>
         </is>

--- a/public/xlsx/pta-school-separation-school-survey.xlsx
+++ b/public/xlsx/pta-school-separation-school-survey.xlsx
@@ -2380,6 +2380,438 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Q32</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>非会員対応</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>応援金・支援金・協力金・協賛金等の依頼文の配布・送信・回収・督促に学校が関与していないか</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>していない／している／要確認</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>L006・L008・L017・P001</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>非会員の特定と学校保有情報の利用が前提となり目的外利用・割当的負担の問題が生じる</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>応援金等の依頼はPTA名義・PTA経路に限定し学校関与を停止する</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>応援金等の依頼文・配布又は送信記録</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>名称変更による実質的会費徴収を含めて確認する</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Q33</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>非会員対応</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>保護者の加入状況を理由に記念品・配布物・登校班・行事参加等で児童生徒に差を設けていないか</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>設けていない／設けている／要確認</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>L006・L008・P001</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>児童生徒への不利益取扱いと加入状況・児童生徒情報の結び付けが生じる</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>非会員児童生徒への不利益禁止を明文化し学校は区別に協力しない</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>卒業記念品・行事・配布物の取扱いが分かる資料</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Q34</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>免除申請</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>免除申請において障害・疾病・ひとり親・介護・就労状況等の資料を学校又は担任が配布・回収・保管していないか</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>していない／している／要確認</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>L008・L010・L012・P001</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>要配慮性の高い私的事情の開示強制と児童生徒の巻き込みが生じる</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>免除手続はPTA自身の責任で会員に対してのみ行わせ学校・担任・児童経由の回収を停止する</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>免除申請書様式・回収経路が分かる資料</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Q35</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>退会</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>退会方法が保護者に明示され退会後に会費引落停止・会員名簿からの削除が行われているか</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>行われている／行われていない／要確認</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>L001・L008・L013</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>退会の自由が形骸化し退会者情報の継続利用が生じる</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>退会手続をPTA名義で明示させ退会後の引落停止・名簿削除を確認する</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>退会届様式・退会案内・退会後処理の説明</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Q36</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>学校施設</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>PTA室等の常時使用について目的外使用許可・使用条件が文書化されているか</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>文書化済み／未文書化／該当なし</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>L003・L018・M001</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>行政財産の根拠不明な常時使用と公私混同が生じる</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>使用許可と条件を文書化し任意加入・個人情報・会費徴収の適正性を条件に含める</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>使用許可書・使用条件が分かる資料</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Q37</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>移行計画</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>分離措置について実施事項・担当・期限を定めた改善計画を作成しているか</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>作成済み／未作成／要確認</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>L001・L008・L015</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>是正が先送りされ混在運用が固定化する</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>期限付き改善計画の提出を求め翌年度入学手続で再確認する</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>改善計画書</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>新たな混在を積み増さないことを移行期間の前提とする</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -2792,7 +3224,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>docs/guideline.md 第9章</t>
+          <t>docs/guideline.md 第12章・第13章</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2829,7 +3261,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -2849,19 +3281,19 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>docs/guideline.md 第8章・第10章</t>
+          <t>docs/guideline.md 第8章・第12章</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>責任回避条文ではなく学校混在の是正根拠として整理</t>
+          <t>責任回避条文ではなく学校混在の是正根拠として整理。第12章で選択的援用への応答に使用</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L006</t>
+          <t>L020</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2871,7 +3303,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>個人情報保護法第61条</t>
+          <t>社会教育法第11条</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2881,44 +3313,44 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2003-05-30</t>
+          <t>1949-06-10</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://laws.e-gov.go.jp/law/415AC0000000057</t>
+          <t>https://laws.e-gov.go.jp/law/324AC0000000207</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>保有個人情報</t>
+          <t>求めに応じた指導助言</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>行政機関等が法令の定める所掌事務又は業務の範囲内で利用目的をできる限り特定して保有する規律</t>
+          <t>文部科学大臣及び教育委員会は社会教育関係団体の求めに応じ専門的技術的指導又は助言を与えることができる旨</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>docs/guideline.md 第5章</t>
+          <t>docs/guideline.md 第12章</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>PPC資料P001が61条の使い方を学校・PTA文脈で説明</t>
+          <t>第12条の干渉禁止と対で使用。分離後も求めに応じた助言という協力関係が残ることの説明に使う</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L007</t>
+          <t>L006</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2928,7 +3360,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>個人情報保護法第62条</t>
+          <t>個人情報保護法第61条</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2953,12 +3385,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>利用目的明示</t>
+          <t>保有個人情報</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>本人から直接書面等で取得するときの利用目的明示</t>
+          <t>行政機関等が法令の定める所掌事務又は業務の範囲内で利用目的をできる限り特定して保有する規律</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -2968,14 +3400,14 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>PPC資料P001が学校保護者への説明文脈で言及</t>
+          <t>PPC資料P001が61条の使い方を学校・PTA文脈で説明</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L008</t>
+          <t>L007</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2985,7 +3417,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>個人情報保護法第69条</t>
+          <t>個人情報保護法第62条</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -3010,12 +3442,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>目的外利用・提供</t>
+          <t>利用目的明示</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>保有個人情報の利用及び提供の制限</t>
+          <t>本人から直接書面等で取得するときの利用目的明示</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -3025,14 +3457,14 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>学校からPTAへの提供問題の中心。PPC資料P001と併用</t>
+          <t>PPC資料P001が学校保護者への説明文脈で言及</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>L009</t>
+          <t>L008</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3042,7 +3474,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>個人情報保護法第70条</t>
+          <t>個人情報保護法第69条</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3067,12 +3499,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>提供先への措置要求</t>
+          <t>目的外利用・提供</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>提供先に対する制限又は措置要求</t>
+          <t>保有個人情報の利用及び提供の制限</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -3082,14 +3514,14 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>PPC資料P001が単なる提供の場合の措置要求として説明</t>
+          <t>学校からPTAへの提供問題の中心。PPC資料P001と併用</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>L010</t>
+          <t>L009</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3099,7 +3531,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>消費者契約法第1条</t>
+          <t>個人情報保護法第70条</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -3109,7 +3541,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2000-05-12</t>
+          <t>2003-05-30</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -3119,34 +3551,34 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://laws.e-gov.go.jp/law/412AC0000000061</t>
+          <t>https://laws.e-gov.go.jp/law/415AC0000000057</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>情報格差・交渉力格差</t>
+          <t>提供先への措置要求</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>消費者と事業者の情報及び交渉力の格差への配慮</t>
+          <t>提供先に対する制限又は措置要求</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>docs/guideline.md 全体</t>
+          <t>docs/guideline.md 第5章</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>PTA入会手続の心理的圧迫の説明に使用</t>
+          <t>PPC資料P001が単なる提供の場合の措置要求として説明</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>L011</t>
+          <t>L010</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3156,7 +3588,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>消費者契約法第3条</t>
+          <t>消費者契約法第1条</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3181,29 +3613,29 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>事業者の努力義務</t>
+          <t>情報格差・交渉力格差</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>契約条項等の明確化・情報提供</t>
+          <t>消費者と事業者の情報及び交渉力の格差への配慮</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>docs/guideline.md 第3章</t>
+          <t>docs/guideline.md 全体</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>PTAの案内文・加入手続の説明に使用</t>
+          <t>PTA入会手続の心理的圧迫の説明に使用</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>L012</t>
+          <t>L011</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3213,7 +3645,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>消費者契約法第4条</t>
+          <t>消費者契約法第3条</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3238,12 +3670,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>誤認・困惑取消し</t>
+          <t>事業者の努力義務</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>不実告知・不利益事実の不告知等</t>
+          <t>契約条項等の明確化・情報提供</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -3253,14 +3685,14 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>学校手続との混在による誤認の説明に使用。適用可否は個別判断として書く</t>
+          <t>PTAの案内文・加入手続の説明に使用</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L013</t>
+          <t>L012</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3270,7 +3702,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>消費者契約法第10条</t>
+          <t>消費者契約法第4条</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3295,12 +3727,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>不当条項</t>
+          <t>誤認・困惑取消し</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>消費者の利益を一方的に害する条項</t>
+          <t>不実告知・不利益事実の不告知等</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -3310,14 +3742,14 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>自動加入・退会制限等の検討用。適用可否は個別判断として書く</t>
+          <t>学校手続との混在による誤認の説明に使用。適用可否は個別判断として書く</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L014</t>
+          <t>L013</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3327,7 +3759,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>地方公務員法第34条</t>
+          <t>消費者契約法第10条</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3337,7 +3769,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1950-12-13</t>
+          <t>2000-05-12</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3347,34 +3779,34 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://laws.e-gov.go.jp/law/325AC0000000261</t>
+          <t>https://laws.e-gov.go.jp/law/412AC0000000061</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>守秘義務</t>
+          <t>不当条項</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>職員の秘密を守る義務</t>
+          <t>消費者の利益を一方的に害する条項</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>docs/guideline.md 第8章・第9章</t>
+          <t>docs/guideline.md 第3章</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>名簿提供・漏えいリスクとの関係で必要に応じて使用</t>
+          <t>自動加入・退会制限等の検討用。適用可否は個別判断として書く</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L015</t>
+          <t>L014</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3384,7 +3816,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>地方公務員法第35条</t>
+          <t>地方公務員法第34条</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3409,29 +3841,29 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>職務専念義務</t>
+          <t>守秘義務</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>勤務時間及び職務上の注意力を職責遂行に用いる義務</t>
+          <t>職員の秘密を守る義務</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>docs/guideline.md 第7章</t>
+          <t>docs/guideline.md 第8章・第9章</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>教職員のPTA本来事務従事の中心論点</t>
+          <t>名簿提供・漏えいリスクとの関係で必要に応じて使用</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L016</t>
+          <t>L015</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3441,7 +3873,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>地方公務員法第38条</t>
+          <t>地方公務員法第35条</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3466,29 +3898,29 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>営利企業従事等制限</t>
+          <t>職務専念義務</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>兼職・兼業関係の確認対象</t>
+          <t>勤務時間及び職務上の注意力を職責遂行に用いる義務</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>docs/guideline.md 第8章</t>
+          <t>docs/guideline.md 第7章</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>第37条ではなく第38条側を確認。PTA役員兼任は35条・服務・利益相反と併せて整理</t>
+          <t>教職員のPTA本来事務従事の中心論点</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L017</t>
+          <t>L016</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3498,7 +3930,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>地方財政法第4条の5</t>
+          <t>地方公務員法第38条</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3508,7 +3940,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1948-07-07</t>
+          <t>1950-12-13</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3518,34 +3950,34 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://laws.e-gov.go.jp/law/323AC0000000109</t>
+          <t>https://laws.e-gov.go.jp/law/325AC0000000261</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>割当的寄附の禁止</t>
+          <t>営利企業従事等制限</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>住民への寄附金等の割当的徴収禁止</t>
+          <t>兼職・兼業関係の確認対象</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>docs/guideline.md 第6章</t>
+          <t>docs/guideline.md 第8章</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>PTA会費と学校徴収金混在の説明に使用。PTA会費そのものとの関係は慎重に書く</t>
+          <t>第37条ではなく第38条側を確認。PTA役員兼任は35条・服務・利益相反と併せて整理</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L018</t>
+          <t>L017</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3555,7 +3987,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>地方自治法第238条の4第7項</t>
+          <t>地方財政法第4条の5</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3565,7 +3997,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1947-04-17</t>
+          <t>1948-07-07</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -3575,54 +4007,54 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://laws.e-gov.go.jp/law/322AC0000000067</t>
+          <t>https://laws.e-gov.go.jp/law/323AC0000000109</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>行政財産の目的外使用</t>
+          <t>割当的寄附の禁止</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>行政財産は用途又は目的を妨げない限度で使用許可できる旨</t>
+          <t>住民への寄附金等の割当的徴収禁止</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>docs/guideline.md 第2章</t>
+          <t>docs/guideline.md 第6章</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>文科省通知M001が学校教育法137条等と併記して説明。学校施設の当然利用ではなく許可・判断の問題として整理</t>
+          <t>PTA会費と学校徴収金混在の説明に使用。PTA会費そのものとの関係は慎重に書く</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M001</t>
+          <t>L018</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>通知・資料</t>
+          <t>法令</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>公立学校施設の目的外使用に係る留意事項の周知について（通知）</t>
+          <t>地方自治法第238条の4第7項</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>文部科学省</t>
+          <t>国</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2024-12-24</t>
+          <t>1947-04-17</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -3632,17 +4064,17 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.mext.go.jp/b_menu/hakusho/nc/mext_00095.html</t>
+          <t>https://laws.e-gov.go.jp/law/322AC0000000067</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>学校施設利用</t>
+          <t>行政財産の目的外使用</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>地方自治法238条の4第7項と学校教育法137条等を踏まえ学校教育上支障のない限り目的外使用可能と説明</t>
+          <t>行政財産は用途又は目的を妨げない限度で使用許可できる旨</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3652,14 +4084,14 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>学校教育上の支障は物理的支障だけでなく教育的配慮や将来の支障も含み得るとの判例言及あり</t>
+          <t>文科省通知M001が学校教育法137条等と併記して説明。学校施設の当然利用ではなく許可・判断の問題として整理</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M002</t>
+          <t>M001</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3669,7 +4101,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>【資料3】学校・教師が担う業務に係る3分類 更なる役割分担・適正化の推進に向けた取組について</t>
+          <t>公立学校施設の目的外使用に係る留意事項の周知について（通知）</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3679,7 +4111,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2023-07-24</t>
+          <t>2024-12-24</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -3689,34 +4121,34 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.mext.go.jp/content/20230725-mext_zaimu-000031116_3.pdf</t>
+          <t>https://www.mext.go.jp/b_menu/hakusho/nc/mext_00095.html</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>教職員の業務適正化</t>
+          <t>学校施設利用</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>学校徴収金の徴収・管理について学校以外が担うべき業務として各教育委員会の権限と責任において取組を進める考え方を示す</t>
+          <t>地方自治法238条の4第7項と学校教育法137条等を踏まえ学校教育上支障のない限り目的外使用可能と説明</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>docs/guideline.md 第6章・第7章</t>
+          <t>docs/guideline.md 第2章</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>PTA会費は学校徴収金ですらないため、PTA会費徴収への教職員関与を見直す補助根拠として使う</t>
+          <t>学校教育上の支障は物理的支障だけでなく教育的配慮や将来の支障も含み得るとの判例言及あり</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P001</t>
+          <t>M002</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3726,17 +4158,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>公立学校とPTAの間で個人情報のやり取りをするためのポイント</t>
+          <t>【資料3】学校・教師が担う業務に係る3分類 更なる役割分担・適正化の推進に向けた取組について</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>個人情報保護委員会事務局</t>
+          <t>文部科学省</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2023-07-24</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -3746,54 +4178,54 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.ppc.go.jp/files/pdf/202603_school_pta_pd_point.pdf</t>
+          <t>https://www.mext.go.jp/content/20230725-mext_zaimu-000031116_3.pdf</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>個人情報</t>
+          <t>教職員の業務適正化</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>公立学校とPTAの個人情報のやり取りにおける利用目的・目的外提供・本人同意・委託/単なる提供・PTA側の個人情報取扱事業者該当性</t>
+          <t>学校徴収金の徴収・管理について学校以外が担うべき業務として各教育委員会の権限と責任において取組を進める考え方を示す</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>docs/guideline.md 第5章</t>
+          <t>docs/guideline.md 第6章・第7章</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>本文・図解ともに中核資料。公立学校側とPTA側双方のポイントを扱う</t>
+          <t>PTA会費は学校徴収金ですらないため、PTA会費徴収への教職員関与を見直す補助根拠として使う</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>C001</t>
+          <t>P001</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>行政資料</t>
+          <t>通知・資料</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>消費者契約法逐条解説 第2条（定義）</t>
+          <t>公立学校とPTAの間で個人情報のやり取りをするためのポイント</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>消費者庁</t>
+          <t>個人情報保護委員会事務局</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2023-09</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3803,106 +4235,106 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.caa.go.jp/policies/policy/consumer_system/consumer_contract_act/annotations/assets/consumer_system_cms203_230915_04.pdf</t>
+          <t>https://www.ppc.go.jp/files/pdf/202603_school_pta_pd_point.pdf</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>消費者契約法</t>
+          <t>個人情報</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>情報・交渉力格差、事業者概念、その他の団体にPTAが含まれる旨</t>
+          <t>公立学校とPTAの個人情報のやり取りにおける利用目的・目的外提供・本人同意・委託/単なる提供・PTA側の個人情報取扱事業者該当性</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>docs/guideline.md 第3章</t>
+          <t>docs/guideline.md 第5章</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>PTA入会に消費者契約法を使う場合は直接適用の断定を避け契約環境・誤認・心理的圧迫の説明に使う</t>
+          <t>本文・図解ともに中核資料。公立学校側とPTA側双方のポイントを扱う</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Y001</t>
+          <t>C001</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>自治体通知</t>
+          <t>行政資料</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>横浜市教育委員会通知 学教第1965号</t>
+          <t>消費者契約法逐条解説 第2条（定義）</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>横浜市教育委員会</t>
+          <t>消費者庁</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>2023-09</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>https://www.caa.go.jp/policies/policy/consumer_system/consumer_contract_act/annotations/assets/consumer_system_cms203_230915_04.pdf</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>任意加入・学校徴収金分離・名簿提供</t>
+          <t>消費者契約法</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>PTA任意加入・加入届・会費分離・個人情報の整理</t>
+          <t>情報・交渉力格差、事業者概念、その他の団体にPTAが含まれる旨</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>docs/guideline.md 全体</t>
+          <t>docs/guideline.md 第3章</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>ユーザー保有資料から正式情報を確認する。公開URL又は文書画像が必要</t>
+          <t>PTA入会に消費者契約法を使う場合は直接適用の断定を避け契約環境・誤認・心理的圧迫の説明に使う</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A001</t>
+          <t>Y001</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>自治体回答</t>
+          <t>自治体通知</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>仙台市教育委員会回答</t>
+          <t>横浜市教育委員会通知 学教第1965号</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>仙台市教育委員会</t>
+          <t>横浜市教育委員会</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3922,77 +4354,134 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>入会意思確認・会費徴収・名簿提供</t>
+          <t>任意加入・学校徴収金分離・名簿提供</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>自治体回答例として使用予定</t>
+          <t>PTA任意加入・加入届・会費分離・個人情報の整理</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>docs/guideline.md 参考資料</t>
+          <t>docs/guideline.md 全体</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>ユーザー保有メール・回答本文から確認する</t>
+          <t>ユーザー保有資料から正式情報を確認する。公開URL又は文書画像が必要。文書番号は「学教第1965号」と「教学第1965号」の表記が混在しており原本で要統一確認</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>A001</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>自治体回答</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>仙台市教育委員会回答</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>仙台市教育委員会</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>要確認</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>入会意思確認・会費徴収・名簿提供</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>自治体回答例として使用予定</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>docs/guideline.md 参考資料</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>ユーザー保有メール・回答本文から確認する</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>A002</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>自治体回答</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>広島市教育委員会回答</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>広島市教育委員会</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>要確認</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>職務専念義務免除・PTA事務</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>職専免の根拠説明例として使用予定</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>docs/guideline.md 第7章</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>回答本文から正確に反映する</t>
         </is>
